--- a/output/lady_lake/Cash_Reconciliation_Report.xlsx
+++ b/output/lady_lake/Cash_Reconciliation_Report.xlsx
@@ -503,7 +503,7 @@
         <v>NSF Transactions:</v>
       </c>
       <c r="B10" t="str">
-        <v>$-4,000.42</v>
+        <v>-$4,000.42</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -517,7 +517,7 @@
         <v>RFMS 06/25/2025</v>
       </c>
       <c r="C11" t="str">
-        <v>$900.00</v>
+        <v>$156.97</v>
       </c>
     </row>
     <row r="12">
@@ -528,7 +528,7 @@
         <v>RFMS 06/25/2025</v>
       </c>
       <c r="C12" t="str">
-        <v>$156.97</v>
+        <v>$900.00</v>
       </c>
     </row>
     <row r="13">
@@ -569,7 +569,7 @@
         <v>Difference:</v>
       </c>
       <c r="B16" t="str">
-        <v>-$0.00</v>
+        <v>$0.00</v>
       </c>
       <c r="C16" t="str">
         <v/>
